--- a/Data/True_data/current_data/preliminary_trial_balance.xlsx
+++ b/Data/True_data/current_data/preliminary_trial_balance.xlsx
@@ -476,7 +476,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -536,13 +535,13 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>508.22</v>
+        <v>570.8</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>508.22</v>
+        <v>570.8</v>
       </c>
     </row>
     <row r="7">
@@ -567,13 +566,13 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>274.51</v>
+        <v>204.26</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>274.51</v>
+        <v>204.26</v>
       </c>
     </row>
     <row r="8">
@@ -601,10 +600,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>10.11</v>
+        <v>2.56</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-10.11</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="9">
@@ -629,13 +628,13 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>98.25</v>
+        <v>90.47</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>98.25</v>
+        <v>90.47</v>
       </c>
     </row>
     <row r="10">
@@ -660,13 +659,13 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>43.98</v>
+        <v>36.53</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>43.98</v>
+        <v>36.53</v>
       </c>
     </row>
     <row r="11">
@@ -691,13 +690,13 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>563.5700000000001</v>
+        <v>430.58</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>563.5700000000001</v>
+        <v>430.58</v>
       </c>
     </row>
     <row r="12">
@@ -725,10 +724,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>194.68</v>
+        <v>150.8</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-194.68</v>
+        <v>-150.8</v>
       </c>
     </row>
     <row r="13">
@@ -753,13 +752,13 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>85.88</v>
+        <v>64.16</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>85.88</v>
+        <v>64.16</v>
       </c>
     </row>
     <row r="14">
@@ -787,10 +786,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>87.53</v>
+        <v>62.98</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-87.53</v>
+        <v>-62.98</v>
       </c>
     </row>
     <row r="15">
@@ -818,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>76.45999999999999</v>
+        <v>205.72</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-76.45999999999999</v>
+        <v>-205.72</v>
       </c>
     </row>
     <row r="16">
@@ -849,10 +848,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>36.37</v>
+        <v>50.98</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-36.37</v>
+        <v>-50.98</v>
       </c>
     </row>
     <row r="17">
@@ -880,10 +879,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>66.04000000000001</v>
+        <v>52.56</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-66.04000000000001</v>
+        <v>-52.56</v>
       </c>
     </row>
     <row r="18">
@@ -911,10 +910,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>325.79</v>
+        <v>284.71</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-325.79</v>
+        <v>-284.71</v>
       </c>
     </row>
     <row r="19">
@@ -942,10 +941,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>102.46</v>
+        <v>131.34</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-102.46</v>
+        <v>-131.34</v>
       </c>
     </row>
     <row r="20">
@@ -973,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>248.24</v>
+        <v>164.32</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-248.24</v>
+        <v>-164.32</v>
       </c>
     </row>
     <row r="21">
@@ -1004,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>255.89</v>
+        <v>184.48</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-255.89</v>
+        <v>-184.48</v>
       </c>
     </row>
     <row r="22">
@@ -1035,10 +1034,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1354.66</v>
+        <v>1406.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-1354.66</v>
+        <v>-1406.5</v>
       </c>
     </row>
     <row r="23">
@@ -1063,13 +1062,13 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>532.49</v>
+        <v>634.85</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>532.49</v>
+        <v>634.85</v>
       </c>
     </row>
     <row r="24">
@@ -1094,13 +1093,13 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>379.27</v>
+        <v>353.65</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>379.27</v>
+        <v>353.65</v>
       </c>
     </row>
     <row r="25">
@@ -1125,13 +1124,13 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>127.3</v>
+        <v>110.38</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>127.3</v>
+        <v>110.38</v>
       </c>
     </row>
     <row r="26">
@@ -1156,13 +1155,13 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>58.45</v>
+        <v>40.4</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>58.45</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="27">
@@ -1187,13 +1186,13 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>19.97</v>
+        <v>20.27</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>19.97</v>
+        <v>20.27</v>
       </c>
     </row>
     <row r="28">
@@ -1218,13 +1217,13 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>43.56</v>
+        <v>60.55</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>43.56</v>
+        <v>60.55</v>
       </c>
     </row>
     <row r="29">
@@ -1252,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.23</v>
+        <v>4.59</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.23</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="30">
@@ -1280,13 +1279,13 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>23.01</v>
+        <v>84.64</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>23.01</v>
+        <v>84.64</v>
       </c>
     </row>
   </sheetData>
